--- a/results/link-prediction-gcn/Link/1shot/MUTAG/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/MUTAG/GCN_total_results.xlsx
@@ -898,387 +898,387 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6679±0.0000</t>
+          <t>0.7110±0.0063</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6177±0.0371</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6780±0.0206</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6913±0.0044</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7007±0.0124</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7104±0.0080</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7151±0.0112</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7151±0.0112</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7151±0.0112</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.7004±0.0227</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.7209±0.0000</t>
+          <t>0.7351±0.0217</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7171±0.0119</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.3357±0.0000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6623±0.0017</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.6404±0.0000</t>
+          <t>0.6125±0.0532</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.7101±0.0073</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.6583±0.0000</t>
+          <t>0.6692±0.0044</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6687±0.0075</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6552±0.0087</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6639±0.0041</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6639±0.0041</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6639±0.0041</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6788±0.0272</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6619±0.0000</t>
+          <t>0.6484±0.0132</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6663±0.0032</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.4452±0.1549</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5768±0.0628</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.5411±0.0354</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5703±0.0425</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.6579±0.0133</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.5536±0.0320</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.7181±0.0130</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6538±0.0421</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6538±0.0421</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6538±0.0421</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.7121±0.0185</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5065±0.0104</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6147±0.0457</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>0.3357±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.4982±0.0000</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.5125±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4679±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.5814±0.0000</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5196±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.5054±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.5349±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.5349±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.5349±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5054±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5116±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5367±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6895±0.0200</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.6702±0.0069</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.6389±0.0310</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.6446±0.0343</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.6933±0.0059</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6800±0.0057</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6887±0.0019</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6887±0.0019</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6887±0.0019</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6798±0.0046</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6567±0.0264</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6962±0.0029</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.3357±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6977±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.5778±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.7227±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.6655±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.7424±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.7030±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7496±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7496±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7496±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.7125±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.7227±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7304±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6986±0.0147</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.6387±0.0097</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.6261±0.0083</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6611±0.0335</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.6496±0.0176</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.6945±0.0128</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6708±0.0199</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6708±0.0199</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6708±0.0199</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.6690±0.0244</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7087±0.0180</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.6956±0.0108</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.3357±0.0000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.7102±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.6643±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.6655±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.6875±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.7102±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.7048±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.7120±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.7120±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.7120±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.7030±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7138±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7156±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.6643±0.0000</t>
-        </is>
-      </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6772±0.0020</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5671±0.0000</t>
+          <t>0.6173±0.0174</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6154±0.0068</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.6609±0.0277</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6688±0.0268</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.6905±0.0000</t>
+          <t>0.6591±0.0203</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6627±0.0259</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6627±0.0259</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6627±0.0259</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6569±0.0260</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.7125±0.0000</t>
+          <t>0.7147±0.0184</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6782±0.0328</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1288,62 +1288,62 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6234±0.0135</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.6554±0.0000</t>
+          <t>0.6143±0.0244</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6495±0.0141</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6651±0.0006</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.7030±0.0000</t>
+          <t>0.6861±0.0039</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6768±0.0000</t>
+          <t>0.6450±0.0226</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.6732±0.0000</t>
+          <t>0.6269±0.0147</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.6732±0.0000</t>
+          <t>0.6269±0.0147</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.6732±0.0000</t>
+          <t>0.6269±0.0147</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.6839±0.0000</t>
+          <t>0.6585±0.0325</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6375±0.0000</t>
+          <t>0.6117±0.0074</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6595±0.0170</t>
         </is>
       </c>
     </row>
@@ -1360,387 +1360,387 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.8000±0.0000</t>
+          <t>0.8011±0.0039</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7264±0.0550</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.8005±0.0050</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7946±0.0017</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8021±0.0056</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8011±0.0061</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8043±0.0069</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8043±0.0069</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8043±0.0069</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.8038±0.0067</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8173±0.0000</t>
+          <t>0.8174±0.0149</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7974±0.0000</t>
+          <t>0.8061±0.0073</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.0000±0.0000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7825±0.0211</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7769±0.0000</t>
+          <t>0.7436±0.0347</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7940±0.0000</t>
+          <t>0.8088±0.0070</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7935±0.0000</t>
+          <t>0.7877±0.0091</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7849±0.0178</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7769±0.0178</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7964±0.0024</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7964±0.0024</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7964±0.0024</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7916±0.0131</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7580±0.0000</t>
+          <t>0.7372±0.0124</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7984±0.0009</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.2661±0.3763</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.6514±0.0749</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6626±0.0467</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6609±0.0480</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.7674±0.0240</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6579±0.0377</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.8067±0.0084</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7515±0.0380</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7515±0.0380</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7515±0.0380</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.7998±0.0164</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.5656±0.0093</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7081±0.0461</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.5589±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6707±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.5669±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.7310±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.5906±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.5610±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.5963±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.5963±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.5963±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.5624±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.5895±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6058±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7951±0.0107</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.7828±0.0119</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.7367±0.0393</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.7574±0.0441</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.7970±0.0019</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7892±0.0034</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7958±0.0007</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7958±0.0007</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7958±0.0007</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7904±0.0038</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7452±0.0269</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7986±0.0010</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7921±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.7287±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.8135±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.7970±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.8227±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7966±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.8263±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.8263±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.8263±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7995±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.8020±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.8147±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.7912±0.0067</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.7371±0.0066</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7244±0.0024</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.7668±0.0344</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.7451±0.0214</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.7850±0.0068</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7671±0.0233</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7671±0.0233</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7671±0.0233</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7630±0.0284</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7934±0.0123</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7879±0.0054</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.8090±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.7983±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.7771±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.7948±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.8103±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.8043±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.8113±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.8113±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.8113±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.8056±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.8049±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.8132±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.7983±0.0000</t>
-        </is>
-      </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7839±0.0000</t>
+          <t>0.7787±0.0030</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7206±0.0000</t>
+          <t>0.7175±0.0187</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7705±0.0000</t>
+          <t>0.7134±0.0057</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7935±0.0000</t>
+          <t>0.7653±0.0354</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.8048±0.0000</t>
+          <t>0.7701±0.0253</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7898±0.0000</t>
+          <t>0.7616±0.0195</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.8043±0.0000</t>
+          <t>0.7650±0.0251</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.8043±0.0000</t>
+          <t>0.7650±0.0251</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.8043±0.0000</t>
+          <t>0.7650±0.0251</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7849±0.0000</t>
+          <t>0.7527±0.0256</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.7995±0.0000</t>
+          <t>0.7988±0.0135</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.8039±0.0000</t>
+          <t>0.7730±0.0320</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.7503±0.0000</t>
+          <t>0.7233±0.0097</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.7891±0.0000</t>
+          <t>0.7580±0.0200</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7845±0.0000</t>
+          <t>0.7405±0.0198</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7989±0.0004</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7976±0.0000</t>
+          <t>0.7848±0.0031</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7822±0.0000</t>
+          <t>0.7495±0.0217</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.7798±0.0000</t>
+          <t>0.7316±0.0142</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.7798±0.0000</t>
+          <t>0.7316±0.0142</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.7798±0.0000</t>
+          <t>0.7316±0.0142</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.7880±0.0000</t>
+          <t>0.7622±0.0304</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7360±0.0000</t>
+          <t>0.7052±0.0068</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.7990±0.0000</t>
+          <t>0.7636±0.0148</t>
         </is>
       </c>
     </row>
@@ -1817,412 +1817,412 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8139±0.0000</t>
+          <t>0.6992±0.0710</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5321±0.0000</t>
+          <t>0.6005±0.0193</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3957±0.0000</t>
+          <t>0.5125±0.0419</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5440±0.0000</t>
+          <t>0.6162±0.0248</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.4872±0.0000</t>
+          <t>0.6002±0.0168</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5493±0.0000</t>
+          <t>0.5695±0.0215</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5515±0.0000</t>
+          <t>0.5892±0.0291</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5495±0.0000</t>
+          <t>0.5824±0.0235</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5495±0.0000</t>
+          <t>0.5824±0.0235</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5495±0.0000</t>
+          <t>0.5824±0.0234</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5582±0.0000</t>
+          <t>0.5561±0.0232</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6401±0.0000</t>
+          <t>0.6417±0.0268</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5844±0.0000</t>
+          <t>0.6201±0.0296</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.7919±0.0000</t>
+          <t>0.7193±0.0385</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6214±0.0000</t>
+          <t>0.6356±0.0221</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4735±0.0000</t>
+          <t>0.4757±0.0399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6652±0.0000</t>
+          <t>0.6836±0.0152</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6172±0.0000</t>
+          <t>0.5654±0.0130</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5975±0.0000</t>
+          <t>0.6381±0.0363</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.6043±0.0000</t>
+          <t>0.6207±0.0476</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6474±0.0088</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6474±0.0088</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6474±0.0088</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.5950±0.0000</t>
+          <t>0.5908±0.0118</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6265±0.0000</t>
+          <t>0.6493±0.0155</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6274±0.0000</t>
+          <t>0.6501±0.0224</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7492±0.0000</t>
+          <t>0.7029±0.0524</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.4242±0.0000</t>
+          <t>0.5453±0.0252</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4542±0.0000</t>
+          <t>0.4591±0.0494</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.4303±0.0000</t>
+          <t>0.4585±0.0117</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5506±0.0000</t>
+          <t>0.5663±0.0397</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.4392±0.0000</t>
+          <t>0.5029±0.0297</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.4348±0.0000</t>
+          <t>0.5879±0.0134</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.4435±0.0000</t>
+          <t>0.5107±0.0413</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.4435±0.0000</t>
+          <t>0.5107±0.0413</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.4435±0.0000</t>
+          <t>0.5107±0.0413</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.4318±0.0000</t>
+          <t>0.5936±0.0205</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4929±0.0000</t>
+          <t>0.5173±0.0049</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.4553±0.0000</t>
+          <t>0.5356±0.0405</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.7910±0.0000</t>
+          <t>0.6505±0.0395</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.6157±0.0000</t>
+          <t>0.6023±0.0113</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4408±0.0000</t>
+          <t>0.5529±0.0397</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6296±0.0000</t>
+          <t>0.5934±0.0132</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5067±0.0000</t>
+          <t>0.5473±0.0359</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6652±0.0000</t>
+          <t>0.5847±0.0143</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.5997±0.0000</t>
+          <t>0.6020±0.0215</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6687±0.0000</t>
+          <t>0.5807±0.0054</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6687±0.0000</t>
+          <t>0.5807±0.0054</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6687±0.0000</t>
+          <t>0.5807±0.0054</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.6125±0.0000</t>
+          <t>0.5918±0.0094</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6396±0.0168</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6412±0.0000</t>
+          <t>0.5970±0.0130</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7643±0.0000</t>
+          <t>0.7044±0.0200</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5839±0.0000</t>
+          <t>0.6118±0.0213</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.1809±0.0000</t>
+          <t>0.5845±0.0175</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4446±0.0000</t>
+          <t>0.6250±0.0151</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.5867±0.0000</t>
+          <t>0.5846±0.0277</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5723±0.0000</t>
+          <t>0.6103±0.0124</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6018±0.0000</t>
+          <t>0.6297±0.0269</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.5772±0.0000</t>
+          <t>0.5960±0.0188</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.5772±0.0000</t>
+          <t>0.5960±0.0188</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.5772±0.0000</t>
+          <t>0.5960±0.0188</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5757±0.0000</t>
+          <t>0.6231±0.0258</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.6236±0.0000</t>
+          <t>0.6412±0.0149</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6223±0.0000</t>
+          <t>0.6308±0.0219</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7766±0.0000</t>
+          <t>0.6983±0.0254</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5804±0.0000</t>
+          <t>0.5815±0.0231</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.2129±0.0000</t>
+          <t>0.5798±0.0326</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6370±0.0000</t>
+          <t>0.6355±0.0181</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.6150±0.0297</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.5930±0.0000</t>
+          <t>0.5854±0.0192</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6104±0.0000</t>
+          <t>0.5831±0.0171</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5789±0.0241</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5789±0.0241</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5789±0.0241</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6122±0.0085</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.6385±0.0158</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6466±0.0000</t>
+          <t>0.6304±0.0225</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7400±0.0000</t>
+          <t>0.7137±0.0298</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5520±0.0000</t>
+          <t>0.5794±0.0296</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5012±0.0000</t>
+          <t>0.4663±0.0134</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5941±0.0000</t>
+          <t>0.6085±0.0182</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2232,42 +2232,42 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6204±0.0000</t>
+          <t>0.6033±0.0040</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5179±0.0000</t>
+          <t>0.5354±0.0036</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5754±0.0000</t>
+          <t>0.5736±0.0069</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5754±0.0000</t>
+          <t>0.5736±0.0069</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5754±0.0000</t>
+          <t>0.5736±0.0069</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5267±0.0000</t>
+          <t>0.5524±0.0186</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5938±0.0000</t>
+          <t>0.5915±0.0095</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6406±0.0000</t>
+          <t>0.5732±0.0107</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8557±0.0000</t>
+          <t>0.7984±0.0432</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6529±0.0000</t>
+          <t>0.7242±0.0207</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6151±0.0000</t>
+          <t>0.6720±0.0183</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7298±0.0275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6902±0.0000</t>
+          <t>0.7284±0.0061</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.6775±0.0113</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6553±0.0000</t>
+          <t>0.7224±0.0282</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6526±0.0000</t>
+          <t>0.7121±0.0160</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6528±0.0000</t>
+          <t>0.7116±0.0156</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6528±0.0000</t>
+          <t>0.7121±0.0160</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6617±0.0000</t>
+          <t>0.6872±0.0354</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.7362±0.0268</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.7253±0.0229</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8730±0.0000</t>
+          <t>0.8084±0.0358</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7018±0.0000</t>
+          <t>0.7589±0.0109</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.6491±0.0227</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7852±0.0000</t>
+          <t>0.8074±0.0143</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7303±0.0000</t>
+          <t>0.7053±0.0213</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6918±0.0000</t>
+          <t>0.7334±0.0385</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6863±0.0000</t>
+          <t>0.7330±0.0500</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6972±0.0000</t>
+          <t>0.7506±0.0137</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6972±0.0000</t>
+          <t>0.7506±0.0137</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6972±0.0000</t>
+          <t>0.7506±0.0137</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6823±0.0000</t>
+          <t>0.7054±0.0148</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7352±0.0000</t>
+          <t>0.7479±0.0129</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7129±0.0000</t>
+          <t>0.7345±0.0218</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8403±0.0000</t>
+          <t>0.8050±0.0402</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6232±0.0000</t>
+          <t>0.6758±0.0075</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.6252±0.0287</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6238±0.0000</t>
+          <t>0.6201±0.0045</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6947±0.0000</t>
+          <t>0.7054±0.0248</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6271±0.0000</t>
+          <t>0.6613±0.0171</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6241±0.0000</t>
+          <t>0.7136±0.0162</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6247±0.0000</t>
+          <t>0.6369±0.0254</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6248±0.0000</t>
+          <t>0.6369±0.0254</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6247±0.0000</t>
+          <t>0.6369±0.0254</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6188±0.0000</t>
+          <t>0.7085±0.0196</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.6932±0.0000</t>
+          <t>0.6896±0.0059</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6367±0.0000</t>
+          <t>0.6551±0.0244</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.8789±0.0000</t>
+          <t>0.7582±0.0279</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7410±0.0000</t>
+          <t>0.6988±0.0165</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6402±0.0000</t>
+          <t>0.6912±0.0197</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7349±0.0000</t>
+          <t>0.7212±0.0145</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6685±0.0000</t>
+          <t>0.6891±0.0207</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7574±0.0000</t>
+          <t>0.7075±0.0072</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6921±0.0000</t>
+          <t>0.7086±0.0298</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7593±0.0000</t>
+          <t>0.7058±0.0017</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7593±0.0000</t>
+          <t>0.7058±0.0017</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7593±0.0000</t>
+          <t>0.7058±0.0017</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7064±0.0000</t>
+          <t>0.7037±0.0197</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7688±0.0000</t>
+          <t>0.7451±0.0088</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7412±0.0000</t>
+          <t>0.7142±0.0081</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.8189±0.0000</t>
+          <t>0.8029±0.0166</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6808±0.0000</t>
+          <t>0.7322±0.0035</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4911±0.0000</t>
+          <t>0.7164±0.0133</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6037±0.0000</t>
+          <t>0.7523±0.0156</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7214±0.0000</t>
+          <t>0.7070±0.0373</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6714±0.0000</t>
+          <t>0.7467±0.0130</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7136±0.0000</t>
+          <t>0.7516±0.0136</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6731±0.0000</t>
+          <t>0.7361±0.0196</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6731±0.0000</t>
+          <t>0.7361±0.0196</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6731±0.0000</t>
+          <t>0.7361±0.0196</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.7465±0.0226</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7318±0.0000</t>
+          <t>0.7360±0.0091</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7041±0.0000</t>
+          <t>0.7387±0.0129</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.8348±0.0000</t>
+          <t>0.7970±0.0204</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7136±0.0252</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5025±0.0000</t>
+          <t>0.7018±0.0231</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7657±0.0000</t>
+          <t>0.7649±0.0254</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7344±0.0000</t>
+          <t>0.7393±0.0256</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7079±0.0000</t>
+          <t>0.7201±0.0207</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7461±0.0000</t>
+          <t>0.7170±0.0162</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7136±0.0000</t>
+          <t>0.7114±0.0204</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7136±0.0000</t>
+          <t>0.7114±0.0204</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7136±0.0000</t>
+          <t>0.7114±0.0204</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7110±0.0000</t>
+          <t>0.7391±0.0016</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7256±0.0000</t>
+          <t>0.7335±0.0086</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7652±0.0000</t>
+          <t>0.7452±0.0214</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.8622±0.0000</t>
+          <t>0.8120±0.0303</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7048±0.0000</t>
+          <t>0.7198±0.0113</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6648±0.0000</t>
+          <t>0.6496±0.0056</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7101±0.0000</t>
+          <t>0.7212±0.0130</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6651±0.0006</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7247±0.0000</t>
+          <t>0.7148±0.0014</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6627±0.0000</t>
+          <t>0.6882±0.0059</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.6978±0.0035</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.6978±0.0035</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.6978±0.0035</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.6638±0.0000</t>
+          <t>0.6948±0.0078</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7337±0.0000</t>
+          <t>0.7227±0.0144</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7360±0.0000</t>
+          <t>0.6991±0.0073</t>
         </is>
       </c>
     </row>
